--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/69.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/69.xlsx
@@ -426,13 +426,13 @@
         <v>-6.433060498414178</v>
       </c>
       <c r="E2">
-        <v>-14.76147785645868</v>
+        <v>-19.77134223656642</v>
       </c>
       <c r="F2">
-        <v>-4.104693188577964</v>
+        <v>-4.396080823665583</v>
       </c>
       <c r="G2">
-        <v>-5.614815496548299</v>
+        <v>-6.052357058291615</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.255597458544528</v>
       </c>
       <c r="E3">
-        <v>-15.9420872580504</v>
+        <v>-21.08401099716983</v>
       </c>
       <c r="F3">
-        <v>-4.444936567450974</v>
+        <v>-4.301620684339198</v>
       </c>
       <c r="G3">
-        <v>-4.560741107389892</v>
+        <v>-6.499141663180575</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.135443694962432</v>
       </c>
       <c r="E4">
-        <v>-15.59805455921368</v>
+        <v>-21.19983577686401</v>
       </c>
       <c r="F4">
-        <v>-4.293474101110177</v>
+        <v>-4.345778364526438</v>
       </c>
       <c r="G4">
-        <v>-4.620128983818878</v>
+        <v>-7.253350147937337</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.07557460077562</v>
       </c>
       <c r="E5">
-        <v>-16.63348108411949</v>
+        <v>-19.19054733118667</v>
       </c>
       <c r="F5">
-        <v>-4.279280136843051</v>
+        <v>-4.19180493245671</v>
       </c>
       <c r="G5">
-        <v>-4.676275836164917</v>
+        <v>-6.119309531277835</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.049987323700049</v>
       </c>
       <c r="E6">
-        <v>-17.91174249921262</v>
+        <v>-20.23917888629884</v>
       </c>
       <c r="F6">
-        <v>-3.503805073847844</v>
+        <v>-4.315047343090293</v>
       </c>
       <c r="G6">
-        <v>-4.80190772883472</v>
+        <v>-6.377535393886527</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.032700810233076</v>
       </c>
       <c r="E7">
-        <v>-17.94622682878103</v>
+        <v>-20.30103331276961</v>
       </c>
       <c r="F7">
-        <v>-3.988204491820773</v>
+        <v>-4.411109400950146</v>
       </c>
       <c r="G7">
-        <v>-5.400778795797799</v>
+        <v>-9.037800404515293</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.000536973705885</v>
       </c>
       <c r="E8">
-        <v>-18.50525335960591</v>
+        <v>-21.93557694889022</v>
       </c>
       <c r="F8">
-        <v>-3.697930201991707</v>
+        <v>-4.214155774041307</v>
       </c>
       <c r="G8">
-        <v>-6.312075976938518</v>
+        <v>-7.622485907202693</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.935966136529512</v>
       </c>
       <c r="E9">
-        <v>-18.81717464925424</v>
+        <v>-21.35288914137525</v>
       </c>
       <c r="F9">
-        <v>-3.830801544591162</v>
+        <v>-3.721854455403294</v>
       </c>
       <c r="G9">
-        <v>-5.525791616451757</v>
+        <v>-8.157112527430675</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.821231141407348</v>
       </c>
       <c r="E10">
-        <v>-19.83874404369659</v>
+        <v>-24.58471612948134</v>
       </c>
       <c r="F10">
-        <v>-3.699654857733621</v>
+        <v>-3.659298071743435</v>
       </c>
       <c r="G10">
-        <v>-5.588936962067816</v>
+        <v>-7.579548131558345</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.65438635091479</v>
       </c>
       <c r="E11">
-        <v>-19.37887750821766</v>
+        <v>-23.64432868857451</v>
       </c>
       <c r="F11">
-        <v>-3.277335919792961</v>
+        <v>-4.266259698659265</v>
       </c>
       <c r="G11">
-        <v>-5.417367939495087</v>
+        <v>-6.2288455515357</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.440328831729838</v>
       </c>
       <c r="E12">
-        <v>-19.06194319784284</v>
+        <v>-23.29902348854163</v>
       </c>
       <c r="F12">
-        <v>-3.409676720910743</v>
+        <v>-4.302399867649593</v>
       </c>
       <c r="G12">
-        <v>-6.203509946523658</v>
+        <v>-7.769100037500396</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.18743577466541</v>
       </c>
       <c r="E13">
-        <v>-20.10855052507359</v>
+        <v>-23.96930556878696</v>
       </c>
       <c r="F13">
-        <v>-3.135747859834928</v>
+        <v>-3.85897884023866</v>
       </c>
       <c r="G13">
-        <v>-5.084783913528825</v>
+        <v>-8.453595054291185</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.916394544856088</v>
       </c>
       <c r="E14">
-        <v>-20.55344592548315</v>
+        <v>-24.1400697951422</v>
       </c>
       <c r="F14">
-        <v>-3.280321997296522</v>
+        <v>-4.351956401302567</v>
       </c>
       <c r="G14">
-        <v>-4.890706491834591</v>
+        <v>-6.527370684993941</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.64988085053838</v>
       </c>
       <c r="E15">
-        <v>-20.14375488200922</v>
+        <v>-25.5687444744001</v>
       </c>
       <c r="F15">
-        <v>-2.796835585783844</v>
+        <v>-4.097195132921316</v>
       </c>
       <c r="G15">
-        <v>-3.86026939782658</v>
+        <v>-6.769129894090297</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.406156876357759</v>
       </c>
       <c r="E16">
-        <v>-21.6590909683519</v>
+        <v>-25.22482045893956</v>
       </c>
       <c r="F16">
-        <v>-2.692556469781734</v>
+        <v>-3.668488317170731</v>
       </c>
       <c r="G16">
-        <v>-3.918452235679271</v>
+        <v>-6.350352504463571</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.206050788805584</v>
       </c>
       <c r="E17">
-        <v>-21.70371002274948</v>
+        <v>-25.90212620237078</v>
       </c>
       <c r="F17">
-        <v>-2.266560166705423</v>
+        <v>-2.973297641852811</v>
       </c>
       <c r="G17">
-        <v>-4.987394284854545</v>
+        <v>-4.026025102432349</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.065268532640721</v>
       </c>
       <c r="E18">
-        <v>-23.08728110089098</v>
+        <v>-26.94715762064686</v>
       </c>
       <c r="F18">
-        <v>-2.187408128757675</v>
+        <v>-3.017038015531333</v>
       </c>
       <c r="G18">
-        <v>-3.743781231936245</v>
+        <v>-4.196352670427852</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.989449806645323</v>
       </c>
       <c r="E19">
-        <v>-23.35813365976375</v>
+        <v>-28.72310738613098</v>
       </c>
       <c r="F19">
-        <v>-1.505267190182976</v>
+        <v>-3.146346019821049</v>
       </c>
       <c r="G19">
-        <v>-3.600206182443593</v>
+        <v>-3.551286251009782</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.983129483953123</v>
       </c>
       <c r="E20">
-        <v>-23.77051914527225</v>
+        <v>-28.92515883940521</v>
       </c>
       <c r="F20">
-        <v>-1.581331001595618</v>
+        <v>-2.9711833944557</v>
       </c>
       <c r="G20">
-        <v>-3.840128038765654</v>
+        <v>-4.847709126370536</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.046417501775375</v>
       </c>
       <c r="E21">
-        <v>-24.54635995463638</v>
+        <v>-32.05203844238354</v>
       </c>
       <c r="F21">
-        <v>-1.192433801441434</v>
+        <v>-3.021142189411195</v>
       </c>
       <c r="G21">
-        <v>-3.253171625198412</v>
+        <v>-4.579200709316869</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.170946943197254</v>
       </c>
       <c r="E22">
-        <v>-24.7015281165092</v>
+        <v>-28.38033813154239</v>
       </c>
       <c r="F22">
-        <v>-1.12592052855185</v>
+        <v>-2.155368966235377</v>
       </c>
       <c r="G22">
-        <v>-3.75461664748628</v>
+        <v>-3.734233618600987</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.348942164588887</v>
       </c>
       <c r="E23">
-        <v>-24.7068400165202</v>
+        <v>-31.77912316360027</v>
       </c>
       <c r="F23">
-        <v>-0.5115637868638756</v>
+        <v>-2.780684952858192</v>
       </c>
       <c r="G23">
-        <v>-3.197776266689787</v>
+        <v>-4.702468872471631</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.571457819172623</v>
       </c>
       <c r="E24">
-        <v>-26.31828390672767</v>
+        <v>-30.46805748279558</v>
       </c>
       <c r="F24">
-        <v>-0.2841792507898684</v>
+        <v>-2.139754417762102</v>
       </c>
       <c r="G24">
-        <v>-4.052098959099649</v>
+        <v>-4.350306280186119</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.823271914135064</v>
       </c>
       <c r="E25">
-        <v>-27.79250597755472</v>
+        <v>-30.32206174502529</v>
       </c>
       <c r="F25">
-        <v>-0.5319516249662853</v>
+        <v>-1.530137707879037</v>
       </c>
       <c r="G25">
-        <v>-4.216864810589176</v>
+        <v>-5.43134175221635</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.090799149392858</v>
       </c>
       <c r="E26">
-        <v>-27.23303112780308</v>
+        <v>-32.78371078051385</v>
       </c>
       <c r="F26">
-        <v>-0.2497368145408913</v>
+        <v>-2.099689825513315</v>
       </c>
       <c r="G26">
-        <v>-4.225823146818444</v>
+        <v>-5.472293200537135</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.36031442515562</v>
       </c>
       <c r="E27">
-        <v>-27.55875067775278</v>
+        <v>-31.48991217110041</v>
       </c>
       <c r="F27">
-        <v>-0.6600243386419581</v>
+        <v>-1.043160016675773</v>
       </c>
       <c r="G27">
-        <v>-3.758943530506107</v>
+        <v>-5.483251106272123</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.613412283671582</v>
       </c>
       <c r="E28">
-        <v>-27.07241521169902</v>
+        <v>-30.90232455470915</v>
       </c>
       <c r="F28">
-        <v>0.2724221117209026</v>
+        <v>-2.399383998127414</v>
       </c>
       <c r="G28">
-        <v>-4.604165533228512</v>
+        <v>-5.520438464314756</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.833678169839654</v>
       </c>
       <c r="E29">
-        <v>-27.37926461045877</v>
+        <v>-32.33806591765602</v>
       </c>
       <c r="F29">
-        <v>-0.320798490819617</v>
+        <v>-1.517330278140879</v>
       </c>
       <c r="G29">
-        <v>-4.119792994286667</v>
+        <v>-5.103130956907465</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.005485121917168</v>
       </c>
       <c r="E30">
-        <v>-28.59789507981889</v>
+        <v>-29.61256081563654</v>
       </c>
       <c r="F30">
-        <v>0.2678174867717624</v>
+        <v>-1.888703772340725</v>
       </c>
       <c r="G30">
-        <v>-4.210316551512498</v>
+        <v>-5.067946478916092</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.111576214474407</v>
       </c>
       <c r="E31">
-        <v>-27.34340815326603</v>
+        <v>-31.97454719516428</v>
       </c>
       <c r="F31">
-        <v>0.01552996703042757</v>
+        <v>-1.88726101625176</v>
       </c>
       <c r="G31">
-        <v>-3.803728590561367</v>
+        <v>-5.766471587702312</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.140672193037908</v>
       </c>
       <c r="E32">
-        <v>-27.07616025970337</v>
+        <v>-31.53663470167455</v>
       </c>
       <c r="F32">
-        <v>0.04580329745701033</v>
+        <v>-1.436121006208975</v>
       </c>
       <c r="G32">
-        <v>-3.755553531873893</v>
+        <v>-3.578637978255241</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.084713451565883</v>
       </c>
       <c r="E33">
-        <v>-28.02302341844117</v>
+        <v>-32.36152341301575</v>
       </c>
       <c r="F33">
-        <v>-0.2360607221081139</v>
+        <v>-1.986388336910946</v>
       </c>
       <c r="G33">
-        <v>-3.24496147226102</v>
+        <v>-5.126079658585693</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.938752460885079</v>
       </c>
       <c r="E34">
-        <v>-28.34064152839115</v>
+        <v>-30.41285538464208</v>
       </c>
       <c r="F34">
-        <v>0.1721402694493614</v>
+        <v>-1.400714884910453</v>
       </c>
       <c r="G34">
-        <v>-4.034490167376266</v>
+        <v>-4.705448363456975</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.707636471684058</v>
       </c>
       <c r="E35">
-        <v>-26.85717684211445</v>
+        <v>-31.77562944590336</v>
       </c>
       <c r="F35">
-        <v>-0.08910073168491041</v>
+        <v>-1.704658932348634</v>
       </c>
       <c r="G35">
-        <v>-4.343950032750718</v>
+        <v>-4.335382340895085</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.400162725035633</v>
       </c>
       <c r="E36">
-        <v>-27.62708987900254</v>
+        <v>-31.88723368782239</v>
       </c>
       <c r="F36">
-        <v>-0.3460997765246776</v>
+        <v>-1.620901477598788</v>
       </c>
       <c r="G36">
-        <v>-3.559804284682327</v>
+        <v>-4.383372009032359</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.029559081487265</v>
       </c>
       <c r="E37">
-        <v>-25.64450584454842</v>
+        <v>-32.1206787871548</v>
       </c>
       <c r="F37">
-        <v>-0.4888296884477424</v>
+        <v>-1.631555859144907</v>
       </c>
       <c r="G37">
-        <v>-3.549518419691811</v>
+        <v>-6.108874691738052</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.616081697506558</v>
       </c>
       <c r="E38">
-        <v>-27.11177217929969</v>
+        <v>-30.26162925939293</v>
       </c>
       <c r="F38">
-        <v>-0.3051657297283142</v>
+        <v>-1.742954525089875</v>
       </c>
       <c r="G38">
-        <v>-3.017401192982597</v>
+        <v>-3.847182811309841</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.177292698311535</v>
       </c>
       <c r="E39">
-        <v>-26.99552172304878</v>
+        <v>-30.2921874019967</v>
       </c>
       <c r="F39">
-        <v>-0.2452818498007601</v>
+        <v>-1.886865881625858</v>
       </c>
       <c r="G39">
-        <v>-2.706683320303221</v>
+        <v>-4.017464031667794</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.730748879945111</v>
       </c>
       <c r="E40">
-        <v>-27.07609686106726</v>
+        <v>-30.30342254600972</v>
       </c>
       <c r="F40">
-        <v>0.002479438434248803</v>
+        <v>-1.658819356479197</v>
       </c>
       <c r="G40">
-        <v>-3.430414922825452</v>
+        <v>-3.290001444322804</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.296276700798814</v>
       </c>
       <c r="E41">
-        <v>-27.8720803228175</v>
+        <v>-29.92537421466438</v>
       </c>
       <c r="F41">
-        <v>-0.6080083097023071</v>
+        <v>-1.379433044818777</v>
       </c>
       <c r="G41">
-        <v>-2.821694982883041</v>
+        <v>-3.687482094495399</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.886740243296634</v>
       </c>
       <c r="E42">
-        <v>-26.0313733790237</v>
+        <v>-30.87021540975776</v>
       </c>
       <c r="F42">
-        <v>-0.08846091449507287</v>
+        <v>-1.580516976755082</v>
       </c>
       <c r="G42">
-        <v>-3.572314836275233</v>
+        <v>-3.929939828700542</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.512945380623943</v>
       </c>
       <c r="E43">
-        <v>-24.77536035673026</v>
+        <v>-29.219636447176</v>
       </c>
       <c r="F43">
-        <v>-0.07561705952085895</v>
+        <v>-1.566655590730198</v>
       </c>
       <c r="G43">
-        <v>-2.362184640941122</v>
+        <v>-2.067605677765693</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.185942385761448</v>
       </c>
       <c r="E44">
-        <v>-25.78420021073704</v>
+        <v>-30.48431923295713</v>
       </c>
       <c r="F44">
-        <v>-0.666386877157236</v>
+        <v>-1.094307382920806</v>
       </c>
       <c r="G44">
-        <v>-2.264070002793741</v>
+        <v>-1.728672025455109</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.908636837190833</v>
       </c>
       <c r="E45">
-        <v>-25.92637165220785</v>
+        <v>-29.19328525692537</v>
       </c>
       <c r="F45">
-        <v>0.1988217548597274</v>
+        <v>-1.204373360337932</v>
       </c>
       <c r="G45">
-        <v>-1.063758885529109</v>
+        <v>-3.328837454043994</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.682187691431424</v>
       </c>
       <c r="E46">
-        <v>-25.84576028639731</v>
+        <v>-30.92916708438961</v>
       </c>
       <c r="F46">
-        <v>-0.3689106846777097</v>
+        <v>-0.8366772312737357</v>
       </c>
       <c r="G46">
-        <v>-2.562608378434139</v>
+        <v>-2.82211211162099</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.507361932049813</v>
       </c>
       <c r="E47">
-        <v>-23.86373325424614</v>
+        <v>-29.86370319139093</v>
       </c>
       <c r="F47">
-        <v>-0.1325425767983722</v>
+        <v>-1.273696919374463</v>
       </c>
       <c r="G47">
-        <v>-2.113284585116557</v>
+        <v>-2.497344283672946</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.378262061431489</v>
       </c>
       <c r="E48">
-        <v>-24.70039599800728</v>
+        <v>-26.8257356470792</v>
       </c>
       <c r="F48">
-        <v>-0.09890228759556514</v>
+        <v>-0.8740709034961343</v>
       </c>
       <c r="G48">
-        <v>-2.618679088232775</v>
+        <v>-4.261222810269871</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.288563866590881</v>
       </c>
       <c r="E49">
-        <v>-25.82011553809187</v>
+        <v>-27.06276503358868</v>
       </c>
       <c r="F49">
-        <v>-0.1410589553586478</v>
+        <v>-1.984761079082832</v>
       </c>
       <c r="G49">
-        <v>-2.391588906420929</v>
+        <v>-4.379180858379643</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.232650697775741</v>
       </c>
       <c r="E50">
-        <v>-24.20719989383191</v>
+        <v>-27.16222843669315</v>
       </c>
       <c r="F50">
-        <v>-0.7123325613230076</v>
+        <v>-1.313565132089735</v>
       </c>
       <c r="G50">
-        <v>-1.650473629271984</v>
+        <v>-4.915270739735983</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.202092353216211</v>
       </c>
       <c r="E51">
-        <v>-22.86361524117813</v>
+        <v>-27.96561595344593</v>
       </c>
       <c r="F51">
-        <v>0.0149732944011506</v>
+        <v>-0.9777862201923483</v>
       </c>
       <c r="G51">
-        <v>-1.537971360210932</v>
+        <v>-3.618662473825029</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.190521653427015</v>
       </c>
       <c r="E52">
-        <v>-23.65291467529305</v>
+        <v>-28.13703680853229</v>
       </c>
       <c r="F52">
-        <v>-0.1644011968463098</v>
+        <v>-1.342417878310169</v>
       </c>
       <c r="G52">
-        <v>-1.590158800092002</v>
+        <v>-3.1265862954133</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.193850633526712</v>
       </c>
       <c r="E53">
-        <v>-22.96150726380194</v>
+        <v>-27.51874160989501</v>
       </c>
       <c r="F53">
-        <v>-0.1531315455520427</v>
+        <v>-1.478485931299938</v>
       </c>
       <c r="G53">
-        <v>-1.477911443037474</v>
+        <v>-3.413951579858657</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.207496336642878</v>
       </c>
       <c r="E54">
-        <v>-23.33375688418046</v>
+        <v>-27.36141336592053</v>
       </c>
       <c r="F54">
-        <v>-0.8317479466119305</v>
+        <v>-0.648850501555575</v>
       </c>
       <c r="G54">
-        <v>-1.104846066217003</v>
+        <v>-2.980160866211335</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.22818127049315</v>
       </c>
       <c r="E55">
-        <v>-22.14073946380772</v>
+        <v>-26.12348706881372</v>
       </c>
       <c r="F55">
-        <v>-0.2275831443427666</v>
+        <v>-1.743306107803102</v>
       </c>
       <c r="G55">
-        <v>-2.13820968248173</v>
+        <v>-4.239601637352891</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.25409726845824</v>
       </c>
       <c r="E56">
-        <v>-22.69914559369355</v>
+        <v>-26.35884091994037</v>
       </c>
       <c r="F56">
-        <v>-0.1772513866441855</v>
+        <v>-1.104976809673121</v>
       </c>
       <c r="G56">
-        <v>-2.84095904737606</v>
+        <v>-4.064205624136764</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.2829862378998</v>
       </c>
       <c r="E57">
-        <v>-22.1942750835264</v>
+        <v>-24.11825160737324</v>
       </c>
       <c r="F57">
-        <v>-0.8557482179074576</v>
+        <v>-1.336290520123334</v>
       </c>
       <c r="G57">
-        <v>-3.003612770811532</v>
+        <v>-3.463828258953316</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.312962280940167</v>
       </c>
       <c r="E58">
-        <v>-21.04970780656172</v>
+        <v>-25.46907276149127</v>
       </c>
       <c r="F58">
-        <v>-0.3095027083777451</v>
+        <v>-1.532951161437816</v>
       </c>
       <c r="G58">
-        <v>-2.264460647167376</v>
+        <v>-4.228011417419902</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.342922792339251</v>
       </c>
       <c r="E59">
-        <v>-20.72795067136873</v>
+        <v>-23.89967575244502</v>
       </c>
       <c r="F59">
-        <v>0.273856157427333</v>
+        <v>-1.01758870911213</v>
       </c>
       <c r="G59">
-        <v>-2.019284955074491</v>
+        <v>-4.751299419175881</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.370908202601393</v>
       </c>
       <c r="E60">
-        <v>-21.87706906471112</v>
+        <v>-24.91435280944768</v>
       </c>
       <c r="F60">
-        <v>-0.7142290491567463</v>
+        <v>-1.520108890169517</v>
       </c>
       <c r="G60">
-        <v>-3.578637978255241</v>
+        <v>-4.268214682448812</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.394453388200625</v>
       </c>
       <c r="E61">
-        <v>-20.96167880032662</v>
+        <v>-23.44940052491434</v>
       </c>
       <c r="F61">
-        <v>-0.6033886395469702</v>
+        <v>-1.583404072638928</v>
       </c>
       <c r="G61">
-        <v>-2.572655884145827</v>
+        <v>-2.788437242395523</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.410855875756213</v>
       </c>
       <c r="E62">
-        <v>-22.20675102941753</v>
+        <v>-24.76996694418712</v>
       </c>
       <c r="F62">
-        <v>-0.9913094850042857</v>
+        <v>-1.103493669083312</v>
       </c>
       <c r="G62">
-        <v>-2.899049189953652</v>
+        <v>-5.067377065083337</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.415383402656592</v>
       </c>
       <c r="E63">
-        <v>-20.33223449868246</v>
+        <v>-24.00183359758405</v>
       </c>
       <c r="F63">
-        <v>-0.7187909140461696</v>
+        <v>-1.222089486560995</v>
       </c>
       <c r="G63">
-        <v>-2.969116886292326</v>
+        <v>-4.812902050570639</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.402998637564967</v>
       </c>
       <c r="E64">
-        <v>-21.02185769141455</v>
+        <v>-23.27772607528356</v>
       </c>
       <c r="F64">
-        <v>-1.185198640966749</v>
+        <v>-1.632567055371915</v>
       </c>
       <c r="G64">
-        <v>-2.253714616346902</v>
+        <v>-5.016116577953261</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.368493813073103</v>
       </c>
       <c r="E65">
-        <v>-20.15036192558641</v>
+        <v>-24.90995566118623</v>
       </c>
       <c r="F65">
-        <v>-0.9225750645682982</v>
+        <v>-2.332012356631662</v>
       </c>
       <c r="G65">
-        <v>-3.604685350558227</v>
+        <v>-5.105709871882558</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.306443269100229</v>
       </c>
       <c r="E66">
-        <v>-19.73308115967561</v>
+        <v>-23.70280034496155</v>
       </c>
       <c r="F66">
-        <v>-1.193068867513525</v>
+        <v>-1.544385518147289</v>
       </c>
       <c r="G66">
-        <v>-3.1892714751994</v>
+        <v>-3.862778791345348</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.214209962612204</v>
       </c>
       <c r="E67">
-        <v>-20.81972472560818</v>
+        <v>-22.53261096206148</v>
       </c>
       <c r="F67">
-        <v>-0.8609308955157332</v>
+        <v>-2.221470475586946</v>
       </c>
       <c r="G67">
-        <v>-2.279997037383175</v>
+        <v>-5.894675774256128</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.090657709410011</v>
       </c>
       <c r="E68">
-        <v>-20.05015132427067</v>
+        <v>-21.63050724041549</v>
       </c>
       <c r="F68">
-        <v>-1.196120668812577</v>
+        <v>-2.08936723035648</v>
       </c>
       <c r="G68">
-        <v>-3.445163403202905</v>
+        <v>-4.496605908657592</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.9350457156251392</v>
       </c>
       <c r="E69">
-        <v>-19.82018635721315</v>
+        <v>-22.1339965660103</v>
       </c>
       <c r="F69">
-        <v>-0.8334227156175077</v>
+        <v>-2.399284224654741</v>
       </c>
       <c r="G69">
-        <v>-3.956463919561183</v>
+        <v>-5.186126333576994</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.7506914172128764</v>
       </c>
       <c r="E70">
-        <v>-19.17131037360208</v>
+        <v>-22.72344991369272</v>
       </c>
       <c r="F70">
-        <v>-1.034946917798304</v>
+        <v>-1.891849012288788</v>
       </c>
       <c r="G70">
-        <v>-3.141493681976638</v>
+        <v>-4.795488581034073</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.5401229545798577</v>
       </c>
       <c r="E71">
-        <v>-19.46347393115495</v>
+        <v>-23.32186511143632</v>
       </c>
       <c r="F71">
-        <v>-1.168625950414633</v>
+        <v>-1.876017496105097</v>
       </c>
       <c r="G71">
-        <v>-4.221423431796753</v>
+        <v>-6.742423723224997</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.3049650543485493</v>
       </c>
       <c r="E72">
-        <v>-20.58032694719268</v>
+        <v>-21.41091247883553</v>
       </c>
       <c r="F72">
-        <v>-1.43060812591733</v>
+        <v>-2.500361087295833</v>
       </c>
       <c r="G72">
-        <v>-3.991926483377856</v>
+        <v>-5.974602275210752</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.05163664944523906</v>
       </c>
       <c r="E73">
-        <v>-18.82738182966753</v>
+        <v>-21.50178989522146</v>
       </c>
       <c r="F73">
-        <v>-1.47166490992214</v>
+        <v>-1.575053983199773</v>
       </c>
       <c r="G73">
-        <v>-3.920567674278865</v>
+        <v>-5.424230700397996</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.2134082872665778</v>
       </c>
       <c r="E74">
-        <v>-19.98839652422807</v>
+        <v>-22.24333204245149</v>
       </c>
       <c r="F74">
-        <v>-1.560821218137719</v>
+        <v>-1.909279279594114</v>
       </c>
       <c r="G74">
-        <v>-3.487180847187335</v>
+        <v>-5.858630554424543</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.4836386808816895</v>
       </c>
       <c r="E75">
-        <v>-19.88889236485753</v>
+        <v>-22.84541983261531</v>
       </c>
       <c r="F75">
-        <v>-1.670140478215715</v>
+        <v>-3.196595424812027</v>
       </c>
       <c r="G75">
-        <v>-3.689544564366365</v>
+        <v>-5.140334867677795</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.7490228578500554</v>
       </c>
       <c r="E76">
-        <v>-21.34631379711612</v>
+        <v>-24.17298727270396</v>
       </c>
       <c r="F76">
-        <v>-1.558619075062301</v>
+        <v>-2.442703897885387</v>
       </c>
       <c r="G76">
-        <v>-2.842511693233978</v>
+        <v>-5.702928976621541</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.001940725415861</v>
       </c>
       <c r="E77">
-        <v>-21.182709088167</v>
+        <v>-23.95284003729507</v>
       </c>
       <c r="F77">
-        <v>-1.452300937694062</v>
+        <v>-2.549817847476134</v>
       </c>
       <c r="G77">
-        <v>-3.239952616860102</v>
+        <v>-6.188069562128497</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.236542450018991</v>
       </c>
       <c r="E78">
-        <v>-21.76238546046686</v>
+        <v>-23.26362440722367</v>
       </c>
       <c r="F78">
-        <v>-1.43512247962929</v>
+        <v>-2.206789521750823</v>
       </c>
       <c r="G78">
-        <v>-3.276103774148944</v>
+        <v>-5.630087043120957</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.445390837158194</v>
       </c>
       <c r="E79">
-        <v>-20.88400641414706</v>
+        <v>-24.31828788971407</v>
       </c>
       <c r="F79">
-        <v>-1.955997020393663</v>
+        <v>-2.32353636257223</v>
       </c>
       <c r="G79">
-        <v>-3.731571939987413</v>
+        <v>-7.068078777377565</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.623831161467284</v>
       </c>
       <c r="E80">
-        <v>-21.68787394914466</v>
+        <v>-23.63436604575763</v>
       </c>
       <c r="F80">
-        <v>-1.275944989921429</v>
+        <v>-2.398771103938139</v>
       </c>
       <c r="G80">
-        <v>-3.327956848930548</v>
+        <v>-6.583613543160619</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.767573536558483</v>
       </c>
       <c r="E81">
-        <v>-21.25052298643187</v>
+        <v>-23.52036624108854</v>
       </c>
       <c r="F81">
-        <v>-1.328242918514028</v>
+        <v>-2.613137577387234</v>
       </c>
       <c r="G81">
-        <v>-3.972175768690564</v>
+        <v>-4.8975692527375</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.871003474823403</v>
       </c>
       <c r="E82">
-        <v>-22.82159100238695</v>
+        <v>-26.90166909923981</v>
       </c>
       <c r="F82">
-        <v>-1.865291847792784</v>
+        <v>-3.074166247166023</v>
       </c>
       <c r="G82">
-        <v>-2.890405355550615</v>
+        <v>-6.564577906309809</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.928859784899592</v>
       </c>
       <c r="E83">
-        <v>-24.16497187371038</v>
+        <v>-25.90373381064351</v>
       </c>
       <c r="F83">
-        <v>-1.492454217474114</v>
+        <v>-2.651408622686786</v>
       </c>
       <c r="G83">
-        <v>-3.452598888484108</v>
+        <v>-5.543589109270879</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.935160183121129</v>
       </c>
       <c r="E84">
-        <v>-24.83027716102128</v>
+        <v>-25.9248681988373</v>
       </c>
       <c r="F84">
-        <v>-1.429746589899331</v>
+        <v>-2.222373979811704</v>
       </c>
       <c r="G84">
-        <v>-3.17441374681915</v>
+        <v>-5.976505838895833</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.885631145136388</v>
       </c>
       <c r="E85">
-        <v>-26.55467930687608</v>
+        <v>-24.49094048973051</v>
       </c>
       <c r="F85">
-        <v>-1.476267951165365</v>
+        <v>-2.784992632948188</v>
       </c>
       <c r="G85">
-        <v>-2.449338062807975</v>
+        <v>-4.780428909375928</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.774144780154542</v>
       </c>
       <c r="E86">
-        <v>-27.21040234318675</v>
+        <v>-26.83049960173527</v>
       </c>
       <c r="F86">
-        <v>-1.234385379288467</v>
+        <v>-2.551878248872121</v>
       </c>
       <c r="G86">
-        <v>-2.691530953369976</v>
+        <v>-5.817374535914146</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.593925967210771</v>
       </c>
       <c r="E87">
-        <v>-27.71118816979898</v>
+        <v>-28.91771855661061</v>
       </c>
       <c r="F87">
-        <v>-1.620741523301328</v>
+        <v>-2.752290689500279</v>
       </c>
       <c r="G87">
-        <v>-3.024684393168993</v>
+        <v>-4.83352012818922</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.343913919220291</v>
       </c>
       <c r="E88">
-        <v>-30.16133488130805</v>
+        <v>-30.00714260558388</v>
       </c>
       <c r="F88">
-        <v>-0.981219694617021</v>
+        <v>-2.71283424032302</v>
       </c>
       <c r="G88">
-        <v>-3.15161070914465</v>
+        <v>-4.136296063799933</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.017768573102384</v>
       </c>
       <c r="E89">
-        <v>-30.68371473622587</v>
+        <v>-32.1967775286167</v>
       </c>
       <c r="F89">
-        <v>-1.253187927769522</v>
+        <v>-1.989417966327181</v>
       </c>
       <c r="G89">
-        <v>-3.355358234359096</v>
+        <v>-5.532859631178101</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.6090323738698799</v>
       </c>
       <c r="E90">
-        <v>-32.47099474367717</v>
+        <v>-33.56882590464568</v>
       </c>
       <c r="F90">
-        <v>-1.167169732825386</v>
+        <v>-3.374574671147985</v>
       </c>
       <c r="G90">
-        <v>-1.80747956201746</v>
+        <v>-3.856230532268669</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.1218298092899731</v>
       </c>
       <c r="E91">
-        <v>-33.63996143859517</v>
+        <v>-33.61040182451011</v>
       </c>
       <c r="F91">
-        <v>-0.6952515011720354</v>
+        <v>-2.338378062558771</v>
       </c>
       <c r="G91">
-        <v>-3.226220473963205</v>
+        <v>-4.880162404292012</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4487934844559981</v>
       </c>
       <c r="E92">
-        <v>-35.34195443082302</v>
+        <v>-36.20364831466156</v>
       </c>
       <c r="F92">
-        <v>-0.8579289809530177</v>
+        <v>-1.972860320981262</v>
       </c>
       <c r="G92">
-        <v>-1.589817813901458</v>
+        <v>-4.170590005041244</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.105246180390874</v>
       </c>
       <c r="E93">
-        <v>-35.87702306991032</v>
+        <v>-38.76928243455125</v>
       </c>
       <c r="F93">
-        <v>-1.184234955917204</v>
+        <v>-1.776883048769292</v>
       </c>
       <c r="G93">
-        <v>-3.200027437656491</v>
+        <v>-3.984891574106905</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.835194702879938</v>
       </c>
       <c r="E94">
-        <v>-38.17166651247</v>
+        <v>-38.59389010776017</v>
       </c>
       <c r="F94">
-        <v>-1.35296377600108</v>
+        <v>-1.78581515013237</v>
       </c>
       <c r="G94">
-        <v>-1.831725997547082</v>
+        <v>-5.251413602156961</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.635922049396273</v>
       </c>
       <c r="E95">
-        <v>-40.4386319218948</v>
+        <v>-42.11433032979711</v>
       </c>
       <c r="F95">
-        <v>-1.108776912017218</v>
+        <v>-2.033556642043437</v>
       </c>
       <c r="G95">
-        <v>-3.824575095822158</v>
+        <v>-4.628792681495151</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.507090302928022</v>
       </c>
       <c r="E96">
-        <v>-43.52437939546147</v>
+        <v>-41.89716283028527</v>
       </c>
       <c r="F96">
-        <v>-0.7731975470651764</v>
+        <v>-1.968382392505357</v>
       </c>
       <c r="G96">
-        <v>-2.960893491172777</v>
+        <v>-5.060262702719443</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.417633447693359</v>
       </c>
       <c r="E97">
-        <v>-44.88508620833824</v>
+        <v>-45.533781052989</v>
       </c>
       <c r="F97">
-        <v>-1.01762355064227</v>
+        <v>-2.168281712416912</v>
       </c>
       <c r="G97">
-        <v>-3.193545389490599</v>
+        <v>-3.346376724311053</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.377370705476358</v>
       </c>
       <c r="E98">
-        <v>-46.82720606329681</v>
+        <v>-47.84510060108192</v>
       </c>
       <c r="F98">
-        <v>-0.8241509093355674</v>
+        <v>-2.074286390776708</v>
       </c>
       <c r="G98">
-        <v>-4.215507486918074</v>
+        <v>-6.620519504832414</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.345320844534918</v>
       </c>
       <c r="E99">
-        <v>-50.39346991381737</v>
+        <v>-47.48593600634857</v>
       </c>
       <c r="F99">
-        <v>-1.031025661951676</v>
+        <v>-1.944603048185034</v>
       </c>
       <c r="G99">
-        <v>-3.090137189025924</v>
+        <v>-5.891563861449213</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.33918676577811</v>
       </c>
       <c r="E100">
-        <v>-52.19762301542126</v>
+        <v>-49.05982752584744</v>
       </c>
       <c r="F100">
-        <v>-1.187724651901874</v>
+        <v>-1.920964653691184</v>
       </c>
       <c r="G100">
-        <v>-4.408965836596465</v>
+        <v>-5.938143237186758</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.278061985641935</v>
       </c>
       <c r="E101">
-        <v>-52.41677851502246</v>
+        <v>-53.22883919161844</v>
       </c>
       <c r="F101">
-        <v>-1.285200959144215</v>
+        <v>-1.808277642984006</v>
       </c>
       <c r="G101">
-        <v>-5.00653916970815</v>
+        <v>-6.517382769101959</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.262251374195747</v>
       </c>
       <c r="E102">
-        <v>-55.6236615361758</v>
+        <v>-54.99390363770662</v>
       </c>
       <c r="F102">
-        <v>-0.900702502170164</v>
+        <v>-1.62887385317711</v>
       </c>
       <c r="G102">
-        <v>-4.103885822970469</v>
+        <v>-6.721368653595232</v>
       </c>
     </row>
   </sheetData>
